--- a/Tabel pertumbuhan.xlsx
+++ b/Tabel pertumbuhan.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="H:\PRIBADI\BINUS\Paper\Posyandu\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{555B69F7-6615-4761-B971-EA5EB02ECABE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C742085F-517C-4A6B-891B-6080116EFE9B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="97" uniqueCount="80">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="124" uniqueCount="103">
   <si>
     <t>1. Tabel Metriks Anak Laki-Laki (0–5 Tahun)</t>
   </si>
@@ -266,13 +266,82 @@
   </si>
   <si>
     <t>99.9 – 118.9 cm</t>
+  </si>
+  <si>
+    <t>Criterion</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Previous Method </t>
+  </si>
+  <si>
+    <t>(Mean ± SD)[12]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Proposed Method </t>
+  </si>
+  <si>
+    <t>(Mean ± SD)</t>
+  </si>
+  <si>
+    <t>Mean Difference</t>
+  </si>
+  <si>
+    <t>t-value</t>
+  </si>
+  <si>
+    <t>p-value</t>
+  </si>
+  <si>
+    <t>Result</t>
+  </si>
+  <si>
+    <t>Naturalness</t>
+  </si>
+  <si>
+    <t>3.40 ± 0.39</t>
+  </si>
+  <si>
+    <t>3.66 ± 0.37</t>
+  </si>
+  <si>
+    <t>+0.26</t>
+  </si>
+  <si>
+    <t>&lt; 0.001</t>
+  </si>
+  <si>
+    <t>Significant</t>
+  </si>
+  <si>
+    <t>Readability</t>
+  </si>
+  <si>
+    <t>3.55 ± 0.45</t>
+  </si>
+  <si>
+    <t>3.75 ± 0.40</t>
+  </si>
+  <si>
+    <t>+0.20</t>
+  </si>
+  <si>
+    <t>Fluency</t>
+  </si>
+  <si>
+    <t>3.40 ± 0.42</t>
+  </si>
+  <si>
+    <t>3.64 ± 0.38</t>
+  </si>
+  <si>
+    <t>+0.24</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -299,6 +368,12 @@
       <name val="Arial"/>
       <family val="2"/>
     </font>
+    <font>
+      <sz val="8"/>
+      <color theme="1"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -308,7 +383,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="4">
     <border>
       <left/>
       <right/>
@@ -325,11 +400,29 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -348,6 +441,39 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="justify" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="justify" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="4" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -968,10 +1094,15 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{07F72711-35F2-4221-813A-1E46DEF11DF2}">
-  <dimension ref="A1:C17"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:M17"/>
+  <sheetFormatPr defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="21.42578125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="27.85546875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="36" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="75.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:13" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1" s="2" t="s">
         <v>40</v>
       </c>
@@ -981,15 +1112,47 @@
       <c r="C1" s="2" t="s">
         <v>42</v>
       </c>
-    </row>
-    <row r="2" spans="1:3" ht="45.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G1" s="16" t="s">
+        <v>80</v>
+      </c>
+      <c r="H1" s="12" t="s">
+        <v>81</v>
+      </c>
+      <c r="I1" s="12" t="s">
+        <v>83</v>
+      </c>
+      <c r="J1" s="16" t="s">
+        <v>85</v>
+      </c>
+      <c r="K1" s="16" t="s">
+        <v>86</v>
+      </c>
+      <c r="L1" s="16" t="s">
+        <v>87</v>
+      </c>
+      <c r="M1" s="16" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="2" spans="1:13" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A2" s="3" t="s">
         <v>43</v>
       </c>
       <c r="B2" s="4"/>
       <c r="C2" s="4"/>
-    </row>
-    <row r="3" spans="1:3" ht="43.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G2" s="17"/>
+      <c r="H2" s="8" t="s">
+        <v>82</v>
+      </c>
+      <c r="I2" s="8" t="s">
+        <v>84</v>
+      </c>
+      <c r="J2" s="17"/>
+      <c r="K2" s="17"/>
+      <c r="L2" s="17"/>
+      <c r="M2" s="17"/>
+    </row>
+    <row r="3" spans="1:13" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A3" s="4" t="s">
         <v>44</v>
       </c>
@@ -999,8 +1162,29 @@
       <c r="C3" s="4" t="s">
         <v>46</v>
       </c>
-    </row>
-    <row r="4" spans="1:3" ht="29.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G3" s="9" t="s">
+        <v>89</v>
+      </c>
+      <c r="H3" s="7" t="s">
+        <v>90</v>
+      </c>
+      <c r="I3" s="7" t="s">
+        <v>91</v>
+      </c>
+      <c r="J3" s="10" t="s">
+        <v>92</v>
+      </c>
+      <c r="K3" s="11">
+        <v>8510</v>
+      </c>
+      <c r="L3" s="10" t="s">
+        <v>93</v>
+      </c>
+      <c r="M3" s="7" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A4" s="4" t="s">
         <v>47</v>
       </c>
@@ -1010,8 +1194,29 @@
       <c r="C4" s="4" t="s">
         <v>49</v>
       </c>
-    </row>
-    <row r="5" spans="1:3" ht="43.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G4" s="9" t="s">
+        <v>95</v>
+      </c>
+      <c r="H4" s="7" t="s">
+        <v>96</v>
+      </c>
+      <c r="I4" s="7" t="s">
+        <v>97</v>
+      </c>
+      <c r="J4" s="10" t="s">
+        <v>98</v>
+      </c>
+      <c r="K4" s="11">
+        <v>9000</v>
+      </c>
+      <c r="L4" s="10" t="s">
+        <v>93</v>
+      </c>
+      <c r="M4" s="7" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A5" s="4" t="s">
         <v>50</v>
       </c>
@@ -1021,8 +1226,29 @@
       <c r="C5" s="4" t="s">
         <v>52</v>
       </c>
-    </row>
-    <row r="6" spans="1:3" ht="57.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G5" s="13" t="s">
+        <v>99</v>
+      </c>
+      <c r="H5" s="8" t="s">
+        <v>100</v>
+      </c>
+      <c r="I5" s="8" t="s">
+        <v>101</v>
+      </c>
+      <c r="J5" s="14" t="s">
+        <v>102</v>
+      </c>
+      <c r="K5" s="15">
+        <v>8573</v>
+      </c>
+      <c r="L5" s="14" t="s">
+        <v>93</v>
+      </c>
+      <c r="M5" s="8" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A6" s="4" t="s">
         <v>53</v>
       </c>
@@ -1033,7 +1259,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="7" spans="1:3" ht="57.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:13" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A7" s="4" t="s">
         <v>56</v>
       </c>
@@ -1044,7 +1270,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="8" spans="1:3" ht="57.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:13" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A8" s="4" t="s">
         <v>59</v>
       </c>
@@ -1055,7 +1281,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="9" spans="1:3" ht="57.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:13" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A9" s="4" t="s">
         <v>62</v>
       </c>
@@ -1066,14 +1292,14 @@
         <v>64</v>
       </c>
     </row>
-    <row r="10" spans="1:3" ht="45.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:13" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A10" s="3" t="s">
         <v>65</v>
       </c>
       <c r="B10" s="4"/>
       <c r="C10" s="4"/>
     </row>
-    <row r="11" spans="1:3" ht="43.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:13" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A11" s="4" t="s">
         <v>44</v>
       </c>
@@ -1084,7 +1310,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="12" spans="1:3" ht="29.25" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:13" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A12" s="4" t="s">
         <v>47</v>
       </c>
@@ -1095,7 +1321,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="13" spans="1:3" ht="43.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:13" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A13" s="4" t="s">
         <v>50</v>
       </c>
@@ -1106,7 +1332,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="14" spans="1:3" ht="57.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:13" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A14" s="4" t="s">
         <v>53</v>
       </c>
@@ -1117,7 +1343,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="15" spans="1:3" ht="57.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:13" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A15" s="4" t="s">
         <v>56</v>
       </c>
@@ -1128,7 +1354,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="16" spans="1:3" ht="57.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:13" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A16" s="4" t="s">
         <v>59</v>
       </c>
@@ -1139,7 +1365,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="17" spans="1:3" ht="57" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="6" t="s">
         <v>62</v>
       </c>
@@ -1151,6 +1377,13 @@
       </c>
     </row>
   </sheetData>
+  <mergeCells count="5">
+    <mergeCell ref="G1:G2"/>
+    <mergeCell ref="J1:J2"/>
+    <mergeCell ref="K1:K2"/>
+    <mergeCell ref="L1:L2"/>
+    <mergeCell ref="M1:M2"/>
+  </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>